--- a/output/pdf_financials_xlsx/TFII.xlsx
+++ b/output/pdf_financials_xlsx/TFII.xlsx
@@ -1093,49 +1093,49 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-8.018000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-50.271</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-38.378</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-74.361</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-64.21599999999999</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-75.705</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-54.882</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-61.075</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-48.306</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-85.64100000000001</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-73.018</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-80.39700000000001</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-80.871</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-158.239</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-159.956</v>
       </c>
     </row>
     <row r="14">
@@ -1973,49 +1973,49 @@
         <v>43.269</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>70.834</v>
+        <v>78.852</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>38.732</v>
+        <v>89.003</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>224.807</v>
+        <v>263.185</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>73.66200000000001</v>
+        <v>148.023</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>170.162</v>
+        <v>234.378</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>202.65</v>
+        <v>278.355</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>198.499</v>
+        <v>253.381</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>122.119</v>
+        <v>183.194</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>397.571</v>
+        <v>445.877</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>428.98</v>
+        <v>514.621</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>911.338</v>
+        <v>984.356</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1067.391</v>
+        <v>1147.788</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>685.376</v>
+        <v>766.247</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>560.723</v>
+        <v>718.962</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>405.36</v>
+        <v>565.316</v>
       </c>
     </row>
     <row r="28">
@@ -2025,55 +2025,55 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>18.18</v>
+        <v>123.006</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>20.045</v>
+        <v>122.602</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>27.57</v>
+        <v>126.432</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>35.043</v>
+        <v>132.593</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>44.221</v>
+        <v>147.631</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>37.853</v>
+        <v>135.896</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>35.678</v>
+        <v>121.713</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>47.13</v>
+        <v>176.226</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>53.647</v>
+        <v>193.086</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>61.2</v>
+        <v>270.757</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>62.101</v>
+        <v>260.593</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>65.925</v>
+        <v>392.292</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>55.243</v>
+        <v>393.032</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>55.679</v>
+        <v>430.593</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>60.028</v>
+        <v>441.975</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>79.98399999999999</v>
+        <v>582.069</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>86.84</v>
+        <v>610.504</v>
       </c>
     </row>
     <row r="29">
@@ -2083,55 +2083,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>197.035</v>
+        <v>301.861</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>63.314</v>
+        <v>165.871</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>98.404</v>
+        <v>205.284</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>73.77500000000001</v>
+        <v>221.596</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>269.028</v>
+        <v>410.816</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>111.515</v>
+        <v>283.919</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>205.84</v>
+        <v>356.091</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>249.78</v>
+        <v>454.581</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>252.146</v>
+        <v>446.467</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>183.319</v>
+        <v>453.951</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>459.672</v>
+        <v>706.47</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>494.905</v>
+        <v>906.913</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>966.581</v>
+        <v>1377.388</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1123.07</v>
+        <v>1578.381</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>745.404</v>
+        <v>1208.222</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>640.707</v>
+        <v>1301.031</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>492.2</v>
+        <v>1175.82</v>
       </c>
     </row>
     <row r="30">
@@ -2141,55 +2141,55 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9.948534316094122</v>
+        <v>15.24132523252462</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3.684566129157095</v>
+        <v>9.652883539334375</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.347284977511342</v>
+        <v>11.15515679569365</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.051624258292952</v>
+        <v>9.166082401093663</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>9.565514823582619</v>
+        <v>14.60690536957089</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.006541820694184</v>
+        <v>10.20072050566894</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.994370931361789</v>
+        <v>12.09984715953921</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6.879356230185496</v>
+        <v>12.51991606403216</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>6.806500655421208</v>
+        <v>12.05205685644008</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4.186335417910771</v>
+        <v>10.36658038335368</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.19636009695228</v>
+        <v>15.67078812216946</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.72702204706967</v>
+        <v>19.6572589603542</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>14.94223412897476</v>
+        <v>21.29283938173861</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>15.2651927453669</v>
+        <v>21.45395228313904</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>11.61628864841919</v>
+        <v>18.8287901639518</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>8.771249890138112</v>
+        <v>17.81105562420307</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>7.119878826085026</v>
+        <v>17.00872799936468</v>
       </c>
     </row>
     <row r="31">
@@ -6271,55 +6271,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>123.006</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>122.602</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>126.432</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>132.593</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>147.631</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>135.896</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>121.713</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>176.226</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>193.086</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>270.757</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>260.593</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>392.292</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>393.032</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>430.593</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>441.975</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>582.069</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>610.504</v>
       </c>
     </row>
     <row r="101">
@@ -6967,55 +6967,55 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>24.167</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>23.085</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>65.271</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>64.886</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>32.729</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>64.14700000000001</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>84.179</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>68.065</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>60.992</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>88.773</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>81.051</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>92.842</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>128.821</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>73.339</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>65.389</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>58.778</v>
       </c>
     </row>
     <row r="113">
@@ -27113,7 +27113,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27202,7 +27206,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -27301,7 +27309,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -27883,7 +27891,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -29792,7 +29804,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -29879,7 +29895,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -29976,7 +29996,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -30655,7 +30675,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -32995,7 +33019,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -36561,7 +36589,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -38727,7 +38759,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -41588,7 +41620,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -47119,7 +47155,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -47220,7 +47260,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -48933,7 +48973,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -50143,7 +50187,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -50244,7 +50292,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -51032,7 +51080,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -52236,7 +52288,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -52337,7 +52393,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -53563,7 +53619,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E460" s="5" t="n">
         <v>104.826</v>
       </c>
@@ -53662,7 +53722,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E461" s="5" t="n">
@@ -55163,7 +55223,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -57585,7 +57649,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E500" s="5" t="n">
         <v>24.167</v>
       </c>
@@ -58897,7 +58965,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -58986,7 +59058,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -59081,7 +59157,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -59580,7 +59656,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -60592,7 +60672,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -61174,7 +61258,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr">
         <is>
           <t>-</t>
@@ -61263,7 +61351,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -61356,7 +61448,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -62284,7 +62376,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -64533,7 +64629,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -65519,7 +65615,11 @@
           <t>Depreciation of property and equipment 20</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -65614,7 +65714,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -67208,7 +67308,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
           <t>-</t>
@@ -68673,7 +68777,11 @@
           <t>Depreciation of property and equipment 19</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -68774,7 +68882,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -69485,7 +69593,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E622" t="inlineStr">
         <is>
           <t>-</t>
@@ -70867,7 +70979,11 @@
           <t>Depreciation of property and equipment 18</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
@@ -70958,7 +71074,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -74565,7 +74681,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E674" s="5" t="n">
         <v>104.826</v>
       </c>
@@ -74664,7 +74784,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E675" s="5" t="n">

--- a/output/pdf_financials_xlsx/TFII.xlsx
+++ b/output/pdf_financials_xlsx/TFII.xlsx
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>11.689</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>17.705</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>482.52</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>-14.193</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -2696,43 +2696,43 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>18.042</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>25.243</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>23.316</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>17.124</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>20.946</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>26.407</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>13.109</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>64.298</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>48.09</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>33.995</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>22.415</v>
       </c>
     </row>
     <row r="41">
@@ -2756,43 +2756,43 @@
         <v>283.89</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>422.085</v>
+        <v>430.977</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>414.985</v>
+        <v>433.027</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>598.277</v>
+        <v>623.52</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>507.872</v>
+        <v>531.188</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>569.181</v>
+        <v>586.3049999999999</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>567.106</v>
+        <v>588.052</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>631.727</v>
+        <v>658.134</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>587.37</v>
+        <v>600.479</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1056.023</v>
+        <v>1125.263</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1030.726</v>
+        <v>1095.024</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>894.771</v>
+        <v>942.861</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>927.654</v>
+        <v>961.649</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>881.432</v>
+        <v>903.847</v>
       </c>
     </row>
     <row r="42">
@@ -3176,43 +3176,43 @@
         <v>15.148</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>20.853</v>
+        <v>11.961</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>57.334</v>
+        <v>39.292</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>37.669</v>
+        <v>12.426</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>310.534</v>
+        <v>287.218</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>61.227</v>
+        <v>44.103</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>85.306</v>
+        <v>64.36</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>77.318</v>
+        <v>50.911</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>96.557</v>
+        <v>83.44799999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>86.943</v>
+        <v>17.703</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>85.72</v>
+        <v>21.422</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>105.672</v>
+        <v>57.582</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>109.395</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>117.544</v>
+        <v>95.129</v>
       </c>
     </row>
     <row r="49">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>1080.464</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -3733,13 +3733,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>346.449</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>413.149</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -6619,55 +6617,55 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-11.14</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>18.572</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-23.716</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-13.204</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>22.313</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>39.382</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>2.568</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>55.051</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>14.659</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-11.649</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>12.647</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>19.6</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>41.94</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-147.453</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>106.631</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>11.566</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>142.457</v>
       </c>
     </row>
     <row r="107">
@@ -7162,31 +7160,31 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>5.757</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>13.404</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>7.914</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>2.426</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>40.686</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>12.93</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>89.22499999999999</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>19.068</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -7220,25 +7218,25 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-1.714</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-1.835</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-2.083</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-4.421</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-4.826</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-7.143</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-6.12</v>
       </c>
       <c r="P116" s="3" t="n">
         <v>0</v>
@@ -7617,13 +7615,13 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>118.733</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>357.729</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -7733,13 +7731,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-84.14</v>
+        <v>34.593</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-112.14</v>
+        <v>-111.19</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-571.853</v>
+        <v>-214.124</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -8225,10 +8223,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0</v>
+        <v>26.042</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>-424.924</v>
+        <v>62.413</v>
       </c>
       <c r="J132" s="3" t="n">
         <v>3.654</v>
@@ -8421,18 +8419,16 @@
         <v>160.744</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>235.725</v>
+        <v>261.767</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-155.875</v>
+        <v>331.462</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>225.834</v>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>347.827</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>251.552</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>229.203</v>
@@ -27689,7 +27685,11 @@
           <t>Net change in non-cash operating working capital 7</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -28079,7 +28079,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -28992,7 +28996,11 @@
           <t>Net change in non-cash operating working capital 7</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -29194,7 +29202,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -30473,7 +30485,11 @@
           <t>Net change in non-cash operating working capital 8</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -31075,7 +31091,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -32568,7 +32588,11 @@
           <t>Net change in non-cash operating working capital 8</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -33215,7 +33239,11 @@
           <t>Purchases of intangible assets 11</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -33714,7 +33742,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -36199,7 +36231,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -36781,7 +36817,11 @@
           <t>Purchases of intangible assets 11</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -37175,7 +37215,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -39244,7 +39288,11 @@
           <t>Net change in non-cash operating working capital 7</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -39638,7 +39686,11 @@
           <t>Purchases of intangible assets 9</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -41222,7 +41274,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -41929,7 +41985,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -43234,7 +43294,11 @@
           <t>Purchases of intangible assets 10</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -44933,7 +44997,11 @@
           <t>Net change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -45024,7 +45092,11 @@
           <t>Net cash from continuing operations</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -48264,7 +48336,11 @@
           <t>Net change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -48363,7 +48439,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -53924,7 +54004,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E463" s="5" t="n">
         <v>8.496</v>
       </c>
@@ -54718,7 +54802,11 @@
           <t>Net change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -54817,7 +54905,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -56738,7 +56830,11 @@
           <t>Net change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E491" s="5" t="n">
         <v>-11.14</v>
       </c>
@@ -56936,7 +57032,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E493" s="5" t="n">
         <v>118.733</v>
       </c>
@@ -63831,7 +63931,11 @@
           <t>Net loss from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -66219,7 +66323,11 @@
           <t>Net income from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>-</t>
@@ -67688,7 +67796,11 @@
           <t>Net income from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -70005,7 +70117,11 @@
           <t>Net income from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
